--- a/docs/downloads/05/tbl_latrine_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_latrine_marovoay_tous.xlsx
@@ -495,12 +495,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -567,12 +561,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -639,12 +627,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -711,12 +693,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -728,12 +704,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_latrine_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_latrine_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
